--- a/AAII_Financials/Quarterly/PTZH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PTZH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>PTZH</t>
   </si>
@@ -656,110 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E7" s="2">
         <v>45169</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45077</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44985</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44895</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44804</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44712</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44620</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44530</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44439</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44347</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44255</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44165</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44074</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43982</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43890</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43799</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43708</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43616</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43524</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43434</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43343</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -779,28 +782,28 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <v>100</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
         <v>100</v>
       </c>
       <c r="N8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
         <v>100</v>
@@ -824,10 +827,13 @@
         <v>100</v>
       </c>
       <c r="X8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y8" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -847,19 +853,19 @@
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9" s="3">
         <v>0</v>
@@ -874,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S9" s="3">
         <v>100</v>
@@ -883,19 +889,22 @@
         <v>100</v>
       </c>
       <c r="U9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W9" s="3">
         <v>100</v>
       </c>
       <c r="X9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y9" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -918,31 +927,31 @@
         <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
       <c r="M10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3">
         <v>100</v>
       </c>
       <c r="R10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10" s="3">
         <v>0</v>
@@ -951,19 +960,22 @@
         <v>0</v>
       </c>
       <c r="U10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W10" s="3">
         <v>0</v>
       </c>
       <c r="X10" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,8 +1000,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,8 +1069,11 @@
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1140,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1192,8 +1211,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1260,8 +1282,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,8 +1308,9 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1319,13 +1345,13 @@
         <v>100</v>
       </c>
       <c r="N17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17" s="3">
         <v>0</v>
       </c>
       <c r="P17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="3">
         <v>100</v>
@@ -1349,10 +1375,13 @@
         <v>100</v>
       </c>
       <c r="X17" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1372,17 +1401,17 @@
         <v>-100</v>
       </c>
       <c r="I18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J18" s="3">
         <v>0</v>
       </c>
       <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
       <c r="M18" s="3">
         <v>0</v>
       </c>
@@ -1419,8 +1448,11 @@
       <c r="X18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,8 +1477,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1513,8 +1546,11 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1525,32 +1561,32 @@
         <v>-100</v>
       </c>
       <c r="F21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-100</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>-100</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>-100</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
       <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
       <c r="O21" s="3">
         <v>0</v>
       </c>
@@ -1581,8 +1617,11 @@
       <c r="X21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1649,8 +1688,11 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1661,32 +1703,32 @@
         <v>-100</v>
       </c>
       <c r="F23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>-100</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
       <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>-100</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
         <v>0</v>
       </c>
@@ -1717,8 +1759,11 @@
       <c r="X23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1785,8 +1830,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,8 +1901,11 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1865,32 +1916,32 @@
         <v>-100</v>
       </c>
       <c r="F26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
       <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
         <v>0</v>
       </c>
@@ -1921,8 +1972,11 @@
       <c r="X26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1933,32 +1987,32 @@
         <v>-100</v>
       </c>
       <c r="F27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
       <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
         <v>0</v>
       </c>
@@ -1989,8 +2043,11 @@
       <c r="X27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,8 +2327,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2329,8 +2398,11 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2341,32 +2413,32 @@
         <v>-100</v>
       </c>
       <c r="F33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
       <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
         <v>0</v>
       </c>
@@ -2397,8 +2469,11 @@
       <c r="X33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,8 +2540,11 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2477,32 +2555,32 @@
         <v>-100</v>
       </c>
       <c r="F35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
       <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
         <v>0</v>
       </c>
@@ -2533,81 +2611,87 @@
       <c r="X35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E38" s="2">
         <v>45169</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45077</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44985</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44895</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44804</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44712</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44620</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44530</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44439</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44347</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44255</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44165</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44074</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43982</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43890</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43799</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43708</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43616</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43524</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43434</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43343</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,8 +2743,9 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2679,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3">
         <v>100</v>
@@ -2694,7 +2780,7 @@
         <v>100</v>
       </c>
       <c r="N41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O41" s="3">
         <v>200</v>
@@ -2703,10 +2789,10 @@
         <v>200</v>
       </c>
       <c r="Q41" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S41" s="3">
         <v>0</v>
@@ -2726,8 +2812,11 @@
       <c r="X41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,8 +2883,11 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2862,8 +2954,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2871,13 +2966,13 @@
         <v>100</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F44" s="3">
         <v>0</v>
       </c>
       <c r="G44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H44" s="3">
         <v>100</v>
@@ -2901,13 +2996,13 @@
         <v>100</v>
       </c>
       <c r="O44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
       </c>
       <c r="Q44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R44" s="3">
         <v>100</v>
@@ -2916,7 +3011,7 @@
         <v>100</v>
       </c>
       <c r="T44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
@@ -2930,8 +3025,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2995,11 +3093,14 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-      <c r="X45" s="3" t="s">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3019,7 +3120,7 @@
         <v>100</v>
       </c>
       <c r="I46" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J46" s="3">
         <v>200</v>
@@ -3031,7 +3132,7 @@
         <v>200</v>
       </c>
       <c r="M46" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N46" s="3">
         <v>300</v>
@@ -3043,19 +3144,19 @@
         <v>300</v>
       </c>
       <c r="Q46" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R46" s="3">
         <v>200</v>
       </c>
       <c r="S46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T46" s="3">
         <v>100</v>
       </c>
       <c r="U46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V46" s="3">
         <v>0</v>
@@ -3066,8 +3167,11 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3134,8 +3238,11 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3143,7 +3250,7 @@
         <v>100</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F48" s="3">
         <v>0</v>
@@ -3202,8 +3309,11 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3270,8 +3380,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,8 +3522,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3447,8 +3566,8 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>8</v>
+      <c r="P52" s="3">
+        <v>0</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>8</v>
@@ -3465,8 +3584,8 @@
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -3474,8 +3593,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,13 +3664,16 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E54" s="3">
         <v>100</v>
@@ -3560,7 +3685,7 @@
         <v>100</v>
       </c>
       <c r="H54" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I54" s="3">
         <v>200</v>
@@ -3572,7 +3697,7 @@
         <v>200</v>
       </c>
       <c r="L54" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M54" s="3">
         <v>300</v>
@@ -3587,19 +3712,19 @@
         <v>300</v>
       </c>
       <c r="Q54" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R54" s="3">
         <v>200</v>
       </c>
       <c r="S54" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T54" s="3">
         <v>100</v>
       </c>
       <c r="U54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V54" s="3">
         <v>0</v>
@@ -3610,8 +3735,11 @@
       <c r="X54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,8 +3791,9 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3730,8 +3860,11 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3774,8 +3907,8 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
@@ -3792,14 +3925,17 @@
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3807,7 +3943,7 @@
         <v>800</v>
       </c>
       <c r="E59" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F59" s="3">
         <v>700</v>
@@ -3816,16 +3952,16 @@
         <v>700</v>
       </c>
       <c r="H59" s="3">
+        <v>700</v>
+      </c>
+      <c r="I59" s="3">
         <v>600</v>
-      </c>
-      <c r="I59" s="3">
-        <v>700</v>
       </c>
       <c r="J59" s="3">
         <v>700</v>
       </c>
       <c r="K59" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L59" s="3">
         <v>600</v>
@@ -3834,7 +3970,7 @@
         <v>600</v>
       </c>
       <c r="N59" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="O59" s="3">
         <v>500</v>
@@ -3846,13 +3982,13 @@
         <v>500</v>
       </c>
       <c r="R59" s="3">
+        <v>500</v>
+      </c>
+      <c r="S59" s="3">
         <v>400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>300</v>
-      </c>
-      <c r="T59" s="3">
-        <v>200</v>
       </c>
       <c r="U59" s="3">
         <v>200</v>
@@ -3861,13 +3997,16 @@
         <v>200</v>
       </c>
       <c r="W59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3875,7 +4014,7 @@
         <v>800</v>
       </c>
       <c r="E60" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F60" s="3">
         <v>700</v>
@@ -3884,16 +4023,16 @@
         <v>700</v>
       </c>
       <c r="H60" s="3">
+        <v>700</v>
+      </c>
+      <c r="I60" s="3">
         <v>600</v>
-      </c>
-      <c r="I60" s="3">
-        <v>700</v>
       </c>
       <c r="J60" s="3">
         <v>700</v>
       </c>
       <c r="K60" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L60" s="3">
         <v>600</v>
@@ -3902,7 +4041,7 @@
         <v>600</v>
       </c>
       <c r="N60" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="O60" s="3">
         <v>500</v>
@@ -3914,13 +4053,13 @@
         <v>500</v>
       </c>
       <c r="R60" s="3">
+        <v>500</v>
+      </c>
+      <c r="S60" s="3">
         <v>400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>300</v>
-      </c>
-      <c r="T60" s="3">
-        <v>200</v>
       </c>
       <c r="U60" s="3">
         <v>200</v>
@@ -3929,13 +4068,16 @@
         <v>200</v>
       </c>
       <c r="W60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X60" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3976,10 +4118,10 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -4002,8 +4144,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4070,8 +4215,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,8 +4428,11 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4286,7 +4443,7 @@
         <v>800</v>
       </c>
       <c r="F66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="G66" s="3">
         <v>700</v>
@@ -4307,7 +4464,7 @@
         <v>700</v>
       </c>
       <c r="M66" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="N66" s="3">
         <v>600</v>
@@ -4316,19 +4473,19 @@
         <v>600</v>
       </c>
       <c r="P66" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Q66" s="3">
         <v>500</v>
       </c>
       <c r="R66" s="3">
+        <v>500</v>
+      </c>
+      <c r="S66" s="3">
         <v>400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>300</v>
-      </c>
-      <c r="T66" s="3">
-        <v>200</v>
       </c>
       <c r="U66" s="3">
         <v>200</v>
@@ -4337,13 +4494,16 @@
         <v>200</v>
       </c>
       <c r="W66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X66" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,8 +4810,11 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4649,22 +4822,22 @@
         <v>-900</v>
       </c>
       <c r="E72" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-800</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-700</v>
       </c>
       <c r="G72" s="3">
         <v>-700</v>
       </c>
       <c r="H72" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="I72" s="3">
         <v>-600</v>
       </c>
       <c r="J72" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="K72" s="3">
         <v>-500</v>
@@ -4673,10 +4846,10 @@
         <v>-500</v>
       </c>
       <c r="M72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N72" s="3">
         <v>-400</v>
-      </c>
-      <c r="N72" s="3">
-        <v>-300</v>
       </c>
       <c r="O72" s="3">
         <v>-300</v>
@@ -4691,7 +4864,7 @@
         <v>-300</v>
       </c>
       <c r="S72" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="T72" s="3">
         <v>-200</v>
@@ -4706,10 +4879,13 @@
         <v>-200</v>
       </c>
       <c r="X72" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,8 +5094,11 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -4924,13 +5109,13 @@
         <v>-700</v>
       </c>
       <c r="F76" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="G76" s="3">
         <v>-600</v>
       </c>
       <c r="H76" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="I76" s="3">
         <v>-500</v>
@@ -4942,13 +5127,13 @@
         <v>-500</v>
       </c>
       <c r="L76" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="M76" s="3">
         <v>-400</v>
       </c>
       <c r="N76" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="O76" s="3">
         <v>-300</v>
@@ -4960,7 +5145,7 @@
         <v>-300</v>
       </c>
       <c r="R76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="S76" s="3">
         <v>-200</v>
@@ -4972,7 +5157,7 @@
         <v>-200</v>
       </c>
       <c r="V76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="W76" s="3">
         <v>-100</v>
@@ -4980,8 +5165,11 @@
       <c r="X76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,81 +5236,87 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E80" s="2">
         <v>45169</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45077</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44985</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44895</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44804</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44712</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44620</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44530</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44439</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44347</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44255</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44165</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44074</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43982</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43890</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43799</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43708</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43616</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43524</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43434</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43343</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5133,32 +5327,32 @@
         <v>-100</v>
       </c>
       <c r="F81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
       <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
         <v>0</v>
       </c>
@@ -5189,8 +5383,11 @@
       <c r="X81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5412,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5283,8 +5481,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,13 +5836,16 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
@@ -5656,28 +5872,28 @@
         <v>0</v>
       </c>
       <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
       <c r="O89" s="3">
         <v>0</v>
       </c>
       <c r="P89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S89" s="3">
         <v>-100</v>
       </c>
       <c r="T89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
@@ -5691,8 +5907,11 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,8 +5936,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5755,8 +5975,8 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>8</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>8</v>
@@ -5773,8 +5993,8 @@
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -5785,8 +6005,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,19 +6147,22 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
@@ -5959,8 +6188,8 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>8</v>
@@ -5977,8 +6206,8 @@
       <c r="T94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -5989,8 +6218,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,13 +6529,16 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -6329,25 +6574,25 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S100" s="3">
         <v>100</v>
       </c>
       <c r="T100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -6355,8 +6600,11 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6423,8 +6671,11 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6456,19 +6707,19 @@
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
       <c r="P102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
@@ -6489,6 +6740,9 @@
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PTZH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PTZH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>PTZH</t>
   </si>
@@ -656,113 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45351</v>
+      </c>
+      <c r="F7" s="2">
         <v>45260</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45169</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45077</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44985</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44895</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44804</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44712</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44620</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44530</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44439</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44347</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44255</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44165</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44074</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43982</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43890</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43799</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43708</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43616</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43524</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43434</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43343</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -785,31 +793,31 @@
         <v>0</v>
       </c>
       <c r="J8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8" s="3">
         <v>100</v>
       </c>
       <c r="N8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
         <v>100</v>
@@ -830,10 +838,16 @@
         <v>100</v>
       </c>
       <c r="Y8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA8" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -856,22 +870,22 @@
         <v>0</v>
       </c>
       <c r="J9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N9" s="3">
         <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9" s="3">
         <v>0</v>
@@ -883,28 +897,34 @@
         <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U9" s="3">
         <v>100</v>
       </c>
       <c r="V9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W9" s="3">
         <v>100</v>
       </c>
       <c r="X9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA9" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -930,52 +950,58 @@
         <v>0</v>
       </c>
       <c r="K10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
       <c r="M10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U10" s="3">
         <v>0</v>
       </c>
       <c r="V10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W10" s="3">
         <v>0</v>
       </c>
       <c r="X10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y10" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1001,8 +1027,10 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1072,8 +1100,14 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,8 +1177,14 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1214,8 +1254,14 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1285,8 +1331,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,8 +1361,10 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1318,7 +1372,7 @@
         <v>100</v>
       </c>
       <c r="E17" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F17" s="3">
         <v>100</v>
@@ -1348,16 +1402,16 @@
         <v>100</v>
       </c>
       <c r="O17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S17" s="3">
         <v>100</v>
@@ -1378,10 +1432,16 @@
         <v>100</v>
       </c>
       <c r="Y17" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1389,7 +1449,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="F18" s="3">
         <v>-100</v>
@@ -1404,19 +1464,19 @@
         <v>-100</v>
       </c>
       <c r="J18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M18" s="3">
         <v>0</v>
       </c>
       <c r="N18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O18" s="3">
         <v>0</v>
@@ -1451,8 +1511,14 @@
       <c r="Y18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,8 +1544,10 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1549,8 +1617,14 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1564,7 +1638,7 @@
         <v>-100</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H21" s="3">
         <v>-100</v>
@@ -1591,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q21" s="3">
         <v>0</v>
@@ -1620,8 +1694,14 @@
       <c r="Y21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1691,8 +1771,14 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1706,7 +1792,7 @@
         <v>-100</v>
       </c>
       <c r="G23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H23" s="3">
         <v>-100</v>
@@ -1733,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="P23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q23" s="3">
         <v>0</v>
@@ -1762,8 +1848,14 @@
       <c r="Y23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1833,8 +1925,14 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,8 +2002,14 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1919,7 +2023,7 @@
         <v>-100</v>
       </c>
       <c r="G26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H26" s="3">
         <v>-100</v>
@@ -1946,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q26" s="3">
         <v>0</v>
@@ -1975,8 +2079,14 @@
       <c r="Y26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1990,7 +2100,7 @@
         <v>-100</v>
       </c>
       <c r="G27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H27" s="3">
         <v>-100</v>
@@ -2017,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="P27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q27" s="3">
         <v>0</v>
@@ -2046,8 +2156,14 @@
       <c r="Y27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2233,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2310,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2387,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,8 +2464,14 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2401,8 +2541,14 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2416,7 +2562,7 @@
         <v>-100</v>
       </c>
       <c r="G33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H33" s="3">
         <v>-100</v>
@@ -2443,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q33" s="3">
         <v>0</v>
@@ -2472,8 +2618,14 @@
       <c r="Y33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,8 +2695,14 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2558,7 +2716,7 @@
         <v>-100</v>
       </c>
       <c r="G35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H35" s="3">
         <v>-100</v>
@@ -2585,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q35" s="3">
         <v>0</v>
@@ -2614,84 +2772,96 @@
       <c r="Y35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45351</v>
+      </c>
+      <c r="F38" s="2">
         <v>45260</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45169</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45077</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44985</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44895</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44804</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44712</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44620</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44530</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44439</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44347</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44255</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44165</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44074</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43982</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43890</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43799</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43708</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43616</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43524</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43434</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43343</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2887,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,8 +2916,10 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2768,10 +2942,10 @@
         <v>0</v>
       </c>
       <c r="J41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3">
         <v>100</v>
@@ -2783,22 +2957,22 @@
         <v>100</v>
       </c>
       <c r="O41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q41" s="3">
         <v>200</v>
       </c>
       <c r="R41" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U41" s="3">
         <v>0</v>
@@ -2815,8 +2989,14 @@
       <c r="Y41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2886,8 +3066,14 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2957,28 +3143,34 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E44" s="3">
         <v>100</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3">
         <v>100</v>
@@ -2999,25 +3191,25 @@
         <v>100</v>
       </c>
       <c r="P44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T44" s="3">
         <v>100</v>
       </c>
       <c r="U44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -3028,8 +3220,14 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3096,11 +3294,17 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-      <c r="Y45" s="3" t="s">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3123,10 +3327,10 @@
         <v>100</v>
       </c>
       <c r="J46" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K46" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L46" s="3">
         <v>200</v>
@@ -3135,10 +3339,10 @@
         <v>200</v>
       </c>
       <c r="N46" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O46" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P46" s="3">
         <v>300</v>
@@ -3147,22 +3351,22 @@
         <v>300</v>
       </c>
       <c r="R46" s="3">
+        <v>300</v>
+      </c>
+      <c r="S46" s="3">
+        <v>300</v>
+      </c>
+      <c r="T46" s="3">
         <v>200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>200</v>
       </c>
-      <c r="T46" s="3">
-        <v>100</v>
-      </c>
-      <c r="U46" s="3">
-        <v>100</v>
-      </c>
       <c r="V46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X46" s="3">
         <v>0</v>
@@ -3170,8 +3374,14 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3241,22 +3451,28 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H48" s="3">
         <v>0</v>
@@ -3312,8 +3528,14 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3383,8 +3605,14 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3682,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,13 +3759,19 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -3569,11 +3809,11 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>8</v>
@@ -3587,17 +3827,23 @@
       <c r="V52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,19 +3913,25 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>100</v>
+      </c>
+      <c r="E54" s="3">
         <v>200</v>
       </c>
-      <c r="E54" s="3">
-        <v>100</v>
-      </c>
       <c r="F54" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G54" s="3">
         <v>100</v>
@@ -3688,10 +3940,10 @@
         <v>100</v>
       </c>
       <c r="I54" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J54" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K54" s="3">
         <v>200</v>
@@ -3700,10 +3952,10 @@
         <v>200</v>
       </c>
       <c r="M54" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N54" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O54" s="3">
         <v>300</v>
@@ -3715,22 +3967,22 @@
         <v>300</v>
       </c>
       <c r="R54" s="3">
+        <v>300</v>
+      </c>
+      <c r="S54" s="3">
+        <v>300</v>
+      </c>
+      <c r="T54" s="3">
         <v>200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>200</v>
       </c>
-      <c r="T54" s="3">
-        <v>100</v>
-      </c>
-      <c r="U54" s="3">
-        <v>100</v>
-      </c>
       <c r="V54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X54" s="3">
         <v>0</v>
@@ -3738,8 +3990,14 @@
       <c r="Y54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +4023,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,8 +4052,10 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3863,8 +4125,14 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3910,11 +4178,11 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
@@ -3928,55 +4196,61 @@
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="3">
         <v>800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>800</v>
-      </c>
-      <c r="F59" s="3">
-        <v>700</v>
-      </c>
-      <c r="G59" s="3">
-        <v>700</v>
       </c>
       <c r="H59" s="3">
         <v>700</v>
       </c>
       <c r="I59" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="J59" s="3">
         <v>700</v>
       </c>
       <c r="K59" s="3">
+        <v>600</v>
+      </c>
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="L59" s="3">
-        <v>600</v>
-      </c>
       <c r="M59" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="N59" s="3">
         <v>600</v>
       </c>
       <c r="O59" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="P59" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Q59" s="3">
         <v>500</v>
@@ -3985,69 +4259,75 @@
         <v>500</v>
       </c>
       <c r="S59" s="3">
+        <v>500</v>
+      </c>
+      <c r="T59" s="3">
+        <v>500</v>
+      </c>
+      <c r="U59" s="3">
         <v>400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>300</v>
-      </c>
-      <c r="U59" s="3">
-        <v>200</v>
-      </c>
-      <c r="V59" s="3">
-        <v>200</v>
       </c>
       <c r="W59" s="3">
         <v>200</v>
       </c>
       <c r="X59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y59" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F60" s="3">
         <v>800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>800</v>
-      </c>
-      <c r="F60" s="3">
-        <v>700</v>
-      </c>
-      <c r="G60" s="3">
-        <v>700</v>
       </c>
       <c r="H60" s="3">
         <v>700</v>
       </c>
       <c r="I60" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="J60" s="3">
         <v>700</v>
       </c>
       <c r="K60" s="3">
+        <v>600</v>
+      </c>
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="L60" s="3">
-        <v>600</v>
-      </c>
       <c r="M60" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="N60" s="3">
         <v>600</v>
       </c>
       <c r="O60" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="P60" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Q60" s="3">
         <v>500</v>
@@ -4056,28 +4336,34 @@
         <v>500</v>
       </c>
       <c r="S60" s="3">
+        <v>500</v>
+      </c>
+      <c r="T60" s="3">
+        <v>500</v>
+      </c>
+      <c r="U60" s="3">
         <v>400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>300</v>
-      </c>
-      <c r="U60" s="3">
-        <v>200</v>
-      </c>
-      <c r="V60" s="3">
-        <v>200</v>
       </c>
       <c r="W60" s="3">
         <v>200</v>
       </c>
       <c r="X60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y60" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4121,13 +4407,13 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -4147,8 +4433,14 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4218,8 +4510,14 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4587,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4664,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,25 +4741,31 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E66" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="F66" s="3">
         <v>800</v>
       </c>
       <c r="G66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="H66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="I66" s="3">
         <v>700</v>
@@ -4467,43 +4783,49 @@
         <v>700</v>
       </c>
       <c r="N66" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O66" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="P66" s="3">
         <v>600</v>
       </c>
       <c r="Q66" s="3">
+        <v>600</v>
+      </c>
+      <c r="R66" s="3">
+        <v>600</v>
+      </c>
+      <c r="S66" s="3">
         <v>500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>300</v>
-      </c>
-      <c r="U66" s="3">
-        <v>200</v>
-      </c>
-      <c r="V66" s="3">
-        <v>200</v>
       </c>
       <c r="W66" s="3">
         <v>200</v>
       </c>
       <c r="X66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y66" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="Z66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4851,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4924,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +5001,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4742,8 +5078,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,49 +5155,55 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-600</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-500</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-500</v>
       </c>
       <c r="M72" s="3">
         <v>-500</v>
       </c>
       <c r="N72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P72" s="3">
         <v>-400</v>
-      </c>
-      <c r="O72" s="3">
-        <v>-300</v>
-      </c>
-      <c r="P72" s="3">
-        <v>-300</v>
       </c>
       <c r="Q72" s="3">
         <v>-300</v>
@@ -4867,10 +5215,10 @@
         <v>-300</v>
       </c>
       <c r="T72" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="U72" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="V72" s="3">
         <v>-200</v>
@@ -4882,10 +5230,16 @@
         <v>-200</v>
       </c>
       <c r="Y72" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+        <v>-200</v>
+      </c>
+      <c r="Z72" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5309,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5386,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,31 +5463,37 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-700</v>
+        <v>-900</v>
       </c>
       <c r="E76" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="F76" s="3">
         <v>-700</v>
       </c>
       <c r="G76" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H76" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I76" s="3">
         <v>-600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-600</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-500</v>
       </c>
       <c r="K76" s="3">
         <v>-500</v>
@@ -5130,16 +5502,16 @@
         <v>-500</v>
       </c>
       <c r="M76" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N76" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O76" s="3">
         <v>-400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-400</v>
-      </c>
-      <c r="O76" s="3">
-        <v>-300</v>
-      </c>
-      <c r="P76" s="3">
-        <v>-300</v>
       </c>
       <c r="Q76" s="3">
         <v>-300</v>
@@ -5148,10 +5520,10 @@
         <v>-300</v>
       </c>
       <c r="S76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="T76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="U76" s="3">
         <v>-200</v>
@@ -5160,16 +5532,22 @@
         <v>-200</v>
       </c>
       <c r="W76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="X76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Y76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,84 +5617,96 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45351</v>
+      </c>
+      <c r="F80" s="2">
         <v>45260</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45169</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45077</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44985</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44895</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44804</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44712</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44620</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44530</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44439</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44347</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44255</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44165</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44074</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43982</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43890</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43799</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43708</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43616</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43524</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43434</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43343</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5330,7 +5720,7 @@
         <v>-100</v>
       </c>
       <c r="G81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H81" s="3">
         <v>-100</v>
@@ -5357,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="P81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q81" s="3">
         <v>0</v>
@@ -5386,8 +5776,14 @@
       <c r="Y81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,8 +5809,10 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5484,8 +5882,14 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5959,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +6036,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +6113,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +6190,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,8 +6267,14 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5848,10 +6282,10 @@
         <v>-100</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G89" s="3">
         <v>0</v>
@@ -5875,31 +6309,31 @@
         <v>0</v>
       </c>
       <c r="N89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O89" s="3">
         <v>0</v>
       </c>
       <c r="P89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
       </c>
       <c r="S89" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="T89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
@@ -5910,8 +6344,14 @@
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,8 +6377,10 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5978,11 +6420,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>8</v>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>8</v>
@@ -5996,11 +6438,11 @@
       <c r="U91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -6008,8 +6450,14 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6527,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,8 +6604,14 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6191,11 +6651,11 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>8</v>
@@ -6209,11 +6669,11 @@
       <c r="U94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -6221,8 +6681,14 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6714,10 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6319,8 +6787,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6864,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6941,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,19 +7018,25 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
@@ -6577,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -6586,10 +7078,10 @@
         <v>100</v>
       </c>
       <c r="T100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V100" s="3">
         <v>100</v>
@@ -6598,13 +7090,19 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6674,8 +7172,14 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6710,22 +7214,22 @@
         <v>0</v>
       </c>
       <c r="N102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
       <c r="P102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
       </c>
       <c r="S102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T102" s="3">
         <v>0</v>
@@ -6743,6 +7247,12 @@
         <v>0</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>
